--- a/authorization_forms/030_promotional_email_authorization_form--authorization_forms.xlsx
+++ b/authorization_forms/030_promotional_email_authorization_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>marketing_outreach</t>
+          <t>marketing_outreach_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Marketing Outreach</t>
+          <t>Marketing Outreach 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>do_not_share_outside</t>
+          <t>do_not_share_outside_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do Not Share Outside</t>
+          <t>Do Not Share Outside 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Time Zone</t>
+          <t>Timezone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Do Not Share Outside (Repeat)</t>
+          <t>Do Not Share Outside Repeat Repeat</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Marketing Outreach (Repeat)</t>
+          <t>Marketing Outreach Repeat Repeat</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'receive_both'}</t>
+          <t>receive_both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'receive_both'}</t>
+          <t>receive both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'no_emails'}</t>
+          <t>no_emails</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'no_emails'}</t>
+          <t>no emails</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_share'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'do_not_share'}</t>
+          <t>do not share</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'est'}</t>
+          <t>est</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>cdt</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'edt'}</t>
+          <t>edt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'edt'}</t>
+          <t>edt</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>cet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>cet</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'cet'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'cet'}</t>
+          <t>gmt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time_zone_choices</t>
+          <t>marketing_outreach_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'gmt'}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'gmt'}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>do not share</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>marketing_outreach_choices</t>
+          <t>do_not_share_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_share'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'do_not_share'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>do_not_share_choices</t>
+          <t>marketing_preferences_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>marketing_preferences_choices</t>
+          <t>do_not_contact_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>do_not_contact_choices</t>
+          <t>do_not_share_outside_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>do_not_share_outside_choices</t>
+          <t>do_share_outside_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1522,114 +1522,114 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>do_share_outside_choices</t>
+          <t>marketing_outreach_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>marketing_outreach_choices</t>
+          <t>marketing_outreach_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>marketing_outreach_choices</t>
+          <t>marketing_outreach_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>do not share</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>marketing_outreach_choices</t>
+          <t>do_not_share_outside_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_share'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'do_not_share'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>do_not_share_outside_choices</t>
+          <t>do_not_share_outside_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>do_not_share_outside_choices</t>
+          <t>marketing_outreach_repeat_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>do not share</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>marketing_outreach_repeat_choices</t>
+          <t>do_not_share_outside_repeat_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'do_not_share'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'do_not_share'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>do_not_share_outside_repeat_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>est</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'est'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'est'}</t>
+          <t>pst</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'pst'}</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'pst'}</t>
+          <t>cdt</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>edt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>edt</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'edt'}</t>
+          <t>cet</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'edt'}</t>
+          <t>cet</t>
         </is>
       </c>
     </row>
@@ -1794,114 +1794,114 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>gmt</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>marketing_preferences_repeat_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'cet'}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'cet'}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>timezone_choices</t>
+          <t>marketing_preferences_repeat_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'gmt'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'gmt'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>marketing_preferences_repeat_choices</t>
+          <t>do_not_share_outside_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>marketing_preferences_repeat_choices</t>
+          <t>do_not_share_outside_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>do_not_share_outside_repeat_repeat_choices</t>
+          <t>timezone_repeat_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>est</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>do_not_share_outside_repeat_repeat_choices</t>
+          <t>timezone_repeat_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>pst</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'est'}</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'est'}</t>
+          <t>cdt</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'pst'}</t>
+          <t>edt</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'pst'}</t>
+          <t>edt</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>cet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>cet</t>
         </is>
       </c>
     </row>
@@ -1964,148 +1964,97 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'edt'}</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'edt'}</t>
+          <t>gmt</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>timezone_repeat_choices</t>
+          <t>marketing_outreach_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'cdt'}</t>
+          <t>receive_newsletter</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'cdt'}</t>
+          <t>receive newsletter</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>timezone_repeat_choices</t>
+          <t>marketing_outreach_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'cet'}</t>
+          <t>receive_automated_emails</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'cet'}</t>
+          <t>receive automated emails</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>timezone_repeat_choices</t>
+          <t>marketing_outreach_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'gmt'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'gmt'}</t>
+          <t>do not share</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>marketing_outreach_repeat_repeat_choices</t>
+          <t>do_share_outside_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'receive_newsletter'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'receive_newsletter'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>marketing_outreach_repeat_repeat_choices</t>
+          <t>do_share_outside_repeat_repeat_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'receive_automated_emails'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'receive_automated_emails'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>marketing_outreach_repeat_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>{'value':_'do_not_share'}</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>{'value': 'do_not_share'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>do_share_outside_repeat_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>do_share_outside_repeat_repeat_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
